--- a/別紙/別紙E9_変更管理台帳.xlsx
+++ b/別紙/別紙E9_変更管理台帳.xlsx
@@ -46,12 +46,18 @@
       <sz val="13.5"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
+        <bgColor rgb="00D5F5E3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -83,7 +89,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -103,6 +109,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -638,26 +647,92 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
-      <c r="P2" s="3" t="n"/>
-      <c r="Q2" s="3" t="n"/>
-      <c r="R2" s="3" t="n"/>
-      <c r="S2" s="3" t="n"/>
-      <c r="T2" s="3" t="n"/>
+      <c r="A2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>CHG-20260929-001</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>軽微変更（Minor Change）</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>退職者 Wai Yan Aung (CODIUM) のアカウント無効化・端末回収</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>AWS IAM / ETRCARS Web / GitLab / MDM 端末</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>退職に伴うアクセス権限剥奪と資産回収</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>CODIUM 開発/保守責任者の退職（後任: Vilaphong Douangmala）</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>IAM / GitLab / Web管理 / MDM</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>対象アカウントの利用ログを CloudTrail から取得済</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>第4章 §4.9 に準ずる</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr"/>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>山田氏（Trello「AWSアカウント使用申請」承認予定）</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>エスブランド／CODIUM</t>
+        </is>
+      </c>
+      <c r="Q2" s="7" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>実施後確認予定</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr"/>
+      <c r="T2" s="7" t="inlineStr"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
     </row>
@@ -4416,7 +4491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="C6:I16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col width="31.140625" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
@@ -4424,11 +4499,6 @@
     <col width="40.5703125" bestFit="1" customWidth="1" style="6" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1" s="6">
       <c r="C6" s="2" t="inlineStr">
         <is>
